--- a/data/trans_orig/P04D$aparatos-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183860</t>
+          <t>186281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228302</t>
+          <t>228025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>133858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171584</t>
+          <t>170549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328692</t>
+          <t>329236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>390056</t>
+          <t>385979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41034</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16814</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25964</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>45547</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>33238</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>60148</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16814</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9801</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26146</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>45547</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>34300</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>60404</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164479</t>
+          <t>161720</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>205116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119961</t>
+          <t>120636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156949</t>
+          <t>156010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>293505</t>
+          <t>296191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>351164</t>
+          <t>353466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205690</t>
+          <t>207030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250390</t>
+          <t>251171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173231</t>
+          <t>173047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211663</t>
+          <t>213552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392760</t>
+          <t>390865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449928</t>
+          <t>450334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>22068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147642</t>
+          <t>146829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189430</t>
+          <t>189131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99853</t>
+          <t>98266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138472</t>
+          <t>136759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257633</t>
+          <t>256400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313825</t>
+          <t>312826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>376608</t>
+          <t>375716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>427503</t>
+          <t>426901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145528</t>
+          <t>145548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177262</t>
+          <t>178602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>537738</t>
+          <t>538441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>594545</t>
+          <t>595291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>16569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167766</t>
+          <t>168438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214808</t>
+          <t>218442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59054</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88815</t>
+          <t>89983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>235921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292117</t>
+          <t>290811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36501</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54002</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>761599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>829937</t>
+          <t>825677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>465027</t>
+          <t>465444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>519223</t>
+          <t>518392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1243840</t>
+          <t>1244207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1328682</t>
+          <t>1329423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37990</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>65984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>250730</t>
+          <t>250510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310544</t>
+          <t>307822</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>198227</t>
+          <t>196871</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>250353</t>
+          <t>249025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>461711</t>
+          <t>459543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>541081</t>
+          <t>539953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>69278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50150</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72373</t>
+          <t>72413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112009</t>
+          <t>111248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358410</t>
+          <t>358543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398164</t>
+          <t>398512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>509043</t>
+          <t>513207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>562203</t>
+          <t>560835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>884721</t>
+          <t>882988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>949284</t>
+          <t>950348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81032</t>
+          <t>80119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115154</t>
+          <t>116755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161508</t>
+          <t>163647</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211942</t>
+          <t>210234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251945</t>
+          <t>249090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>315930</t>
+          <t>312345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72451</t>
+          <t>71547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131060</t>
+          <t>130148</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163014</t>
+          <t>164138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>734971</t>
+          <t>735245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>796952</t>
+          <t>797027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>881314</t>
+          <t>880220</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>948677</t>
+          <t>952814</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51586</t>
+          <t>52354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82236</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113050</t>
+          <t>113923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241944</t>
+          <t>243000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299850</t>
+          <t>301882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>335786</t>
+          <t>334381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>397536</t>
+          <t>401047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>37775</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47238</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>77589</t>
+          <t>77952</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2103978</t>
+          <t>2099301</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2217758</t>
+          <t>2220127</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2244861</t>
+          <t>2242538</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2363020</t>
+          <t>2360867</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4378247</t>
+          <t>4380377</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4543143</t>
+          <t>4555235</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127049</t>
+          <t>129689</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76420</t>
+          <t>76958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118156</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>175867</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232546</t>
+          <t>231176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>964584</t>
+          <t>959257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1067163</t>
+          <t>1071189</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>950137</t>
+          <t>952920</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1059144</t>
+          <t>1061610</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1932729</t>
+          <t>1932517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2103039</t>
+          <t>2098898</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119145</t>
+          <t>118858</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>168057</t>
+          <t>167453</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>136213</t>
+          <t>135024</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>187076</t>
+          <t>187717</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>268148</t>
+          <t>268063</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>335081</t>
+          <t>341391</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182066</t>
+          <t>181858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223884</t>
+          <t>224064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>126328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164296</t>
+          <t>163546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317020</t>
+          <t>316165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374656</t>
+          <t>375258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45977</t>
+          <t>46997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,82 +4286,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12439</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30244</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>53756</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>40045</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>69921</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20510</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12872</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30782</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>53756</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>41053</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>69523</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127737</t>
+          <t>130108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169117</t>
+          <t>170999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128701</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168892</t>
+          <t>168838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270756</t>
+          <t>274485</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327148</t>
+          <t>329456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>57933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59763</t>
+          <t>60918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96480</t>
+          <t>95881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175195</t>
+          <t>175130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214734</t>
+          <t>215223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,82 +4629,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>46,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>57,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>183366</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>163684</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202681</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>49,26%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>43,97%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>54,44%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>378137</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>348097</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>407641</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>50,45%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>46,44%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183366</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>163452</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204320</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>49,26%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>378137</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>349614</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>407157</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>50,45%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23967</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43956</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106361</t>
+          <t>107370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143197</t>
+          <t>144068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162335</t>
+          <t>163229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238977</t>
+          <t>239322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295973</t>
+          <t>295415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>54034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>59662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94364</t>
+          <t>93903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252560</t>
+          <t>254078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298797</t>
+          <t>297976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>79359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105093</t>
+          <t>104649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340907</t>
+          <t>342223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>392496</t>
+          <t>396071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,82 +5198,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>13734</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>7681</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7318</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>13734</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>7559</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>22171</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138163</t>
+          <t>136627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181398</t>
+          <t>177677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69154</t>
+          <t>70648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188617</t>
+          <t>188216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239307</t>
+          <t>238732</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>95650</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76820</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>114677</t>
+          <t>112529</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>591794</t>
+          <t>592425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>661057</t>
+          <t>661613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>408167</t>
+          <t>407194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>462780</t>
+          <t>463337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,47 +5576,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>56,1%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1062636</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1019416</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1107084</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>53,79%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>56,04%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1062636</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1019458</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1106854</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>292158</t>
+          <t>295572</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>357312</t>
+          <t>355455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>230966</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>283346</t>
+          <t>285031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>543989</t>
+          <t>543494</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625186</t>
+          <t>625971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>165749</t>
+          <t>162825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216110</t>
+          <t>216215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106219</t>
+          <t>107843</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148497</t>
+          <t>147801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283068</t>
+          <t>282206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>351474</t>
+          <t>348972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>333984</t>
+          <t>337098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>385785</t>
+          <t>386119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>412481</t>
+          <t>413078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>466655</t>
+          <t>468089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>763295</t>
+          <t>760080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>837260</t>
+          <t>834210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102639</t>
+          <t>103082</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146960</t>
+          <t>143777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135498</t>
+          <t>134709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182219</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246709</t>
+          <t>249461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310331</t>
+          <t>308868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110699</t>
+          <t>112444</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152629</t>
+          <t>153939</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109135</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150697</t>
+          <t>152385</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233659</t>
+          <t>231252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>293407</t>
+          <t>293705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119118</t>
+          <t>120583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>154343</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>519250</t>
+          <t>517914</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>587403</t>
+          <t>585633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>644376</t>
+          <t>648061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>720690</t>
+          <t>724041</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40079</t>
+          <t>38934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>56243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>74111</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106111</t>
+          <t>105256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300003</t>
+          <t>300090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>360047</t>
+          <t>361757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>384566</t>
+          <t>385446</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>454886</t>
+          <t>454363</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153688</t>
+          <t>149233</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>206020</t>
+          <t>204334</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195286</t>
+          <t>198539</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253560</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1738953</t>
+          <t>1739278</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1854354</t>
+          <t>1852156</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1785900</t>
+          <t>1776769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1905994</t>
+          <t>1904468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3555272</t>
+          <t>3566976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3720990</t>
+          <t>3738352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76866</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116107</t>
+          <t>116788</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70459</t>
+          <t>70133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>107902</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>156464</t>
+          <t>154647</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>212920</t>
+          <t>209459</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>910224</t>
+          <t>918855</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1020006</t>
+          <t>1024531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1036191</t>
+          <t>1035900</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1150203</t>
+          <t>1145841</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1978580</t>
+          <t>1987150</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2137748</t>
+          <t>2144320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>486038</t>
+          <t>486029</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>576785</t>
+          <t>570879</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>475688</t>
+          <t>473840</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>561346</t>
+          <t>559848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>981727</t>
+          <t>984070</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1104254</t>
+          <t>1108861</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239475</t>
+          <t>240592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284416</t>
+          <t>285426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203147</t>
+          <t>207751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241868</t>
+          <t>243222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457041</t>
+          <t>457136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>515287</t>
+          <t>517099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>53621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84275</t>
+          <t>84377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77576</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111703</t>
+          <t>113115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150339</t>
+          <t>152738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112716</t>
+          <t>112426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152958</t>
+          <t>152625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94385</t>
+          <t>93458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125841</t>
+          <t>124775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216869</t>
+          <t>214339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>266371</t>
+          <t>265182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>57430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>64425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76589</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112020</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244280</t>
+          <t>244727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>289974</t>
+          <t>289687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200809</t>
+          <t>199571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234175</t>
+          <t>232643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454570</t>
+          <t>456587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>510670</t>
+          <t>512023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>38248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>40250</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87595</t>
+          <t>86191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128905</t>
+          <t>126009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76945</t>
+          <t>79242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104903</t>
+          <t>106133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174396</t>
+          <t>175034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224720</t>
+          <t>224073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66041</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38559</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>63158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82500</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119583</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>111772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>446827</t>
+          <t>448088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95496</t>
+          <t>94172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115642</t>
+          <t>115896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>159767</t>
+          <t>145462</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>550242</t>
+          <t>551006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42913</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>19552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58236</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115392</t>
+          <t>113518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533503</t>
+          <t>525836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139367</t>
+          <t>136674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632261</t>
+          <t>646768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74292</t>
+          <t>73649</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>99072</t>
+          <t>98911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>674273</t>
+          <t>673743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>742748</t>
+          <t>740061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624204</t>
+          <t>624595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>823241</t>
+          <t>846637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1333901</t>
+          <t>1335083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1601734</t>
+          <t>1602118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61084</t>
+          <t>62651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62384</t>
+          <t>62851</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62871</t>
+          <t>62613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110947</t>
+          <t>110178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>132231</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180708</t>
+          <t>183173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72639</t>
+          <t>63620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179062</t>
+          <t>179470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195689</t>
+          <t>203054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337640</t>
+          <t>336576</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100599</t>
+          <t>99304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152668</t>
+          <t>151125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>44476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120267</t>
+          <t>120861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148955</t>
+          <t>148942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251949</t>
+          <t>252191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313002</t>
+          <t>313065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355329</t>
+          <t>357248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>404102</t>
+          <t>428828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634867</t>
+          <t>638426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>747246</t>
+          <t>751762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973222</t>
+          <t>972752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48640</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82620</t>
+          <t>83646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67950</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113760</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129011</t>
+          <t>127592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184055</t>
+          <t>183366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78340</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>77515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356816</t>
+          <t>326272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139931</t>
+          <t>140148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>408882</t>
+          <t>389732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124710</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>176859</t>
+          <t>176736</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>520471</t>
+          <t>521401</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>568833</t>
+          <t>569563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>658568</t>
+          <t>659734</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>730655</t>
+          <t>733319</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>54567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44718</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83710</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70277</t>
+          <t>67911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81773</t>
+          <t>81075</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>118732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113273</t>
+          <t>111681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172036</t>
+          <t>170391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -10203,12 +10203,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50288</t>
+          <t>47585</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>62787</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>95790</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>81428</t>
+          <t>82065</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>129773</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1557003</t>
+          <t>1560358</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2183686</t>
+          <t>2185806</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2245111</t>
+          <t>2235527</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2567345</t>
+          <t>2568334</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3826395</t>
+          <t>3878975</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4611785</t>
+          <t>4614320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>152226</t>
+          <t>150620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>234567</t>
+          <t>231520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165780</t>
+          <t>170554</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>235354</t>
+          <t>236938</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>348209</t>
+          <t>345031</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>454978</t>
+          <t>452661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>605709</t>
+          <t>599932</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1410439</t>
+          <t>1397069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>453751</t>
+          <t>445836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>611098</t>
+          <t>611692</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1138177</t>
+          <t>1137263</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2087390</t>
+          <t>2124200</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>266203</t>
+          <t>266319</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>396028</t>
+          <t>399716</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>353643</t>
+          <t>351857</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>672730</t>
+          <t>679644</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>677779</t>
+          <t>667398</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1008507</t>
+          <t>978106</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D$aparatos-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186281</t>
+          <t>183203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228025</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133858</t>
+          <t>134581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170549</t>
+          <t>172848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>329236</t>
+          <t>328617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385979</t>
+          <t>385627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60148</t>
+          <t>59089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161720</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>205116</t>
+          <t>205718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120636</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156010</t>
+          <t>155975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>296191</t>
+          <t>293990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>353466</t>
+          <t>352393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>48017</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207030</t>
+          <t>206627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251171</t>
+          <t>249224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173047</t>
+          <t>172574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213552</t>
+          <t>211745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390865</t>
+          <t>391410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>448072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>146194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189131</t>
+          <t>187913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98266</t>
+          <t>100255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136759</t>
+          <t>136321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256400</t>
+          <t>258682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312826</t>
+          <t>312723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>375716</t>
+          <t>377536</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426901</t>
+          <t>426304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145548</t>
+          <t>146403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178602</t>
+          <t>178859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>538441</t>
+          <t>535000</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>595291</t>
+          <t>592893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>167404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218442</t>
+          <t>214266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>58645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89983</t>
+          <t>89737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235921</t>
+          <t>236763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290811</t>
+          <t>291506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36453</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>52941</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>761599</t>
+          <t>765043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>825677</t>
+          <t>827451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>465444</t>
+          <t>460795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>518392</t>
+          <t>515432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1244207</t>
+          <t>1244446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1329423</t>
+          <t>1324818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>36665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65984</t>
+          <t>66548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>250510</t>
+          <t>246982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>307822</t>
+          <t>306719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196871</t>
+          <t>196324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249025</t>
+          <t>247708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>459543</t>
+          <t>460740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>539953</t>
+          <t>539168</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69278</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52096</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72413</t>
+          <t>73328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>112543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358543</t>
+          <t>360721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398512</t>
+          <t>398950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513207</t>
+          <t>511604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>560835</t>
+          <t>561248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>882988</t>
+          <t>882395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950348</t>
+          <t>948940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>24484</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80119</t>
+          <t>79426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116755</t>
+          <t>115104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163647</t>
+          <t>163188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210234</t>
+          <t>212536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249090</t>
+          <t>253696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312345</t>
+          <t>312496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44680</t>
+          <t>44258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>42098</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71547</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,19 +2980,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130148</t>
+          <t>129542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164138</t>
+          <t>163205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>735245</t>
+          <t>736833</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>797027</t>
+          <t>799703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>880220</t>
+          <t>880153</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>952814</t>
+          <t>948790</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52354</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>82619</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113923</t>
+          <t>114590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>243000</t>
+          <t>240737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>301882</t>
+          <t>298406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>334381</t>
+          <t>333033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401047</t>
+          <t>400693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>65179</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>77952</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2099301</t>
+          <t>2099752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2220127</t>
+          <t>2216449</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2242538</t>
+          <t>2252192</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2360867</t>
+          <t>2363411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4380377</t>
+          <t>4385582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4555235</t>
+          <t>4546687</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129689</t>
+          <t>130141</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>77345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115668</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>175604</t>
+          <t>175354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>231176</t>
+          <t>234629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>959257</t>
+          <t>957819</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1071189</t>
+          <t>1071722</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>952920</t>
+          <t>949511</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1061610</t>
+          <t>1055854</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1932517</t>
+          <t>1941907</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2098898</t>
+          <t>2089338</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>118858</t>
+          <t>117114</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>167453</t>
+          <t>168671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>135024</t>
+          <t>136634</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>187717</t>
+          <t>184753</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>268063</t>
+          <t>267403</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>341391</t>
+          <t>336973</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181858</t>
+          <t>181901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224064</t>
+          <t>223596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163546</t>
+          <t>162339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316165</t>
+          <t>318946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375258</t>
+          <t>372794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22192</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69921</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130108</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170999</t>
+          <t>172848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130888</t>
+          <t>130465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168838</t>
+          <t>168166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>274485</t>
+          <t>273740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>329456</t>
+          <t>327713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23615</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>46149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>61566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>94136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175130</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215223</t>
+          <t>215042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163684</t>
+          <t>162329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202681</t>
+          <t>202575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348097</t>
+          <t>349978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407641</t>
+          <t>404249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,82 +4742,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13906</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7547</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23049</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>31377</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>20765</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>43335</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13906</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>7399</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23755</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>31377</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>21504</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>44210</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107370</t>
+          <t>105756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144068</t>
+          <t>144736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124311</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163229</t>
+          <t>164095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239322</t>
+          <t>238909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295415</t>
+          <t>292425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>54951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>46967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93903</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254078</t>
+          <t>251907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297976</t>
+          <t>300149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79359</t>
+          <t>78733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104649</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>342223</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>396071</t>
+          <t>398244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136627</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177677</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70648</t>
+          <t>70587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188216</t>
+          <t>191571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238732</t>
+          <t>242773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95650</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112529</t>
+          <t>114438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>592425</t>
+          <t>593831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>661613</t>
+          <t>662848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407194</t>
+          <t>407744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>463337</t>
+          <t>466558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019416</t>
+          <t>1016249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1107084</t>
+          <t>1106690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32928</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>295572</t>
+          <t>293124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>355455</t>
+          <t>356100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>229784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>285031</t>
+          <t>283995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>543494</t>
+          <t>540129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625971</t>
+          <t>623433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162825</t>
+          <t>163803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216215</t>
+          <t>216619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107843</t>
+          <t>108103</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147801</t>
+          <t>149046</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282206</t>
+          <t>281802</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348972</t>
+          <t>351339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>337098</t>
+          <t>335267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>386119</t>
+          <t>385309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>413078</t>
+          <t>413170</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>468089</t>
+          <t>466721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>760080</t>
+          <t>764128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>834210</t>
+          <t>837388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,82 +6110,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6852</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>21068</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>18560</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>11490</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>29160</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>12339</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>20552</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>11648</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>29632</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103082</t>
+          <t>102797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143777</t>
+          <t>142586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134709</t>
+          <t>134592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180409</t>
+          <t>179999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249461</t>
+          <t>250834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>308868</t>
+          <t>312010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112444</t>
+          <t>113308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153939</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>109882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152385</t>
+          <t>152525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231252</t>
+          <t>232003</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>290314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,19 +6406,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>119492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152448</t>
+          <t>154043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>517914</t>
+          <t>517183</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>585633</t>
+          <t>585014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>648061</t>
+          <t>648676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>724041</t>
+          <t>723921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74111</t>
+          <t>74332</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105256</t>
+          <t>107405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300090</t>
+          <t>298791</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>361757</t>
+          <t>359970</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>385446</t>
+          <t>385133</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>454363</t>
+          <t>457278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>149233</t>
+          <t>155275</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>204334</t>
+          <t>204408</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>198539</t>
+          <t>196533</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253560</t>
+          <t>253046</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1739278</t>
+          <t>1734941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1852156</t>
+          <t>1858964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1776769</t>
+          <t>1780863</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1904468</t>
+          <t>1902977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3566976</t>
+          <t>3557302</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3738352</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116788</t>
+          <t>115576</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107902</t>
+          <t>108656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>154647</t>
+          <t>157217</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>209459</t>
+          <t>208131</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>918855</t>
+          <t>915772</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1024531</t>
+          <t>1030277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1035900</t>
+          <t>1035312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1145841</t>
+          <t>1145577</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1987150</t>
+          <t>1983208</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2144320</t>
+          <t>2140852</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>486029</t>
+          <t>487038</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>570879</t>
+          <t>573918</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>473840</t>
+          <t>474288</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>559848</t>
+          <t>561646</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>984070</t>
+          <t>980261</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1108861</t>
+          <t>1102442</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7579,32 +7579,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240592</t>
+          <t>261692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285426</t>
+          <t>310661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>245328</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207751</t>
+          <t>226535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243222</t>
+          <t>264812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7649,32 +7649,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>487001</t>
+          <t>531540</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457136</t>
+          <t>503194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>517099</t>
+          <t>561221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53621</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84377</t>
+          <t>85993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7727,32 +7727,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>65346</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76210</t>
+          <t>78145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7762,32 +7762,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130435</t>
+          <t>134363</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113115</t>
+          <t>116790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>156551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131122</t>
+          <t>140766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112426</t>
+          <t>120450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152625</t>
+          <t>163799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108677</t>
+          <t>116530</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>99923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>124775</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239799</t>
+          <t>257296</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214339</t>
+          <t>230498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265182</t>
+          <t>283183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57430</t>
+          <t>70436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64425</t>
+          <t>75016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>93076</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>135886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>268235</t>
+          <t>289292</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244727</t>
+          <t>264309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>289687</t>
+          <t>310187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>238660</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>221016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232643</t>
+          <t>256170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8105,32 +8105,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>485762</t>
+          <t>527951</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456587</t>
+          <t>496888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>512023</t>
+          <t>557636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -8148,32 +8148,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8183,32 +8183,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8218,32 +8218,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>44163</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>91019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126009</t>
+          <t>131073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91087</t>
+          <t>101796</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>87929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106133</t>
+          <t>118275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>211219</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175034</t>
+          <t>184361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224073</t>
+          <t>237605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>41656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66596</t>
+          <t>72528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63158</t>
+          <t>68976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>111223</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119699</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -8491,32 +8491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>277952</t>
+          <t>310575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111772</t>
+          <t>287671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>448088</t>
+          <t>330854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8526,32 +8526,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105583</t>
+          <t>117289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94172</t>
+          <t>105246</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115896</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>383535</t>
+          <t>427864</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145462</t>
+          <t>403762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>551006</t>
+          <t>451821</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -8604,32 +8604,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8639,32 +8639,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8674,32 +8674,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59493</t>
+          <t>56622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -8717,32 +8717,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>321696</t>
+          <t>82833</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113518</t>
+          <t>66786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525836</t>
+          <t>101363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8752,32 +8752,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>19763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>346822</t>
+          <t>111318</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136674</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646768</t>
+          <t>131819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -8830,32 +8830,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73649</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8865,32 +8865,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>37561</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8900,32 +8900,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>75575</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>61602</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98911</t>
+          <t>95322</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -8947,32 +8947,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>709875</t>
+          <t>760465</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>673743</t>
+          <t>724929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>740061</t>
+          <t>794016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>705294</t>
+          <t>547976</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624595</t>
+          <t>523343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>846637</t>
+          <t>572097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1415170</t>
+          <t>1308442</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1335083</t>
+          <t>1269345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1602118</t>
+          <t>1348968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -9060,32 +9060,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62651</t>
+          <t>64072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>47164</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62851</t>
+          <t>59815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9130,32 +9130,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>94175</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62613</t>
+          <t>78078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110178</t>
+          <t>114368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -9173,32 +9173,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>154102</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132231</t>
+          <t>149251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183173</t>
+          <t>206282</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9208,32 +9208,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136046</t>
+          <t>150069</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63620</t>
+          <t>131680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179470</t>
+          <t>171366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>290148</t>
+          <t>325513</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>203054</t>
+          <t>292451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336576</t>
+          <t>358803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -9286,32 +9286,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
+          <t>142499</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99304</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151125</t>
+          <t>171323</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9321,32 +9321,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89999</t>
+          <t>113731</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>96869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120861</t>
+          <t>130499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9356,32 +9356,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>213576</t>
+          <t>256230</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148942</t>
+          <t>225509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252191</t>
+          <t>285760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -9403,32 +9403,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>334922</t>
+          <t>388357</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313065</t>
+          <t>365170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>357248</t>
+          <t>411927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>575198</t>
+          <t>606898</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>428828</t>
+          <t>585714</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>638426</t>
+          <t>628550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>910121</t>
+          <t>995255</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751762</t>
+          <t>963146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>972752</t>
+          <t>1027296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -9516,32 +9516,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9551,32 +9551,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9586,32 +9586,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -9629,32 +9629,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49032</t>
+          <t>50977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83646</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>94375</t>
+          <t>101183</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>85461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115978</t>
+          <t>118330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9699,32 +9699,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>169575</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127592</t>
+          <t>145765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183366</t>
+          <t>194959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -9742,32 +9742,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>79192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80207</t>
+          <t>118031</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9777,32 +9777,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>146526</t>
+          <t>96767</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77515</t>
+          <t>82881</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326272</t>
+          <t>113894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9812,39 +9812,39 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>209348</t>
+          <t>194319</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140148</t>
+          <t>168856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>389732</t>
+          <t>223166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>152206</t>
+          <t>158417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>134324</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>176736</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9894,32 +9894,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>546493</t>
+          <t>606664</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>521401</t>
+          <t>581823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>569563</t>
+          <t>632630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>698699</t>
+          <t>765082</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>659734</t>
+          <t>730492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>733319</t>
+          <t>800636</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -9972,32 +9972,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10007,32 +10007,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>58403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>57869</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44210</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82538</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10085,32 +10085,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>64788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10120,32 +10120,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>103568</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81075</t>
+          <t>86662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118732</t>
+          <t>127100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>139305</t>
+          <t>143512</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111681</t>
+          <t>118626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170391</t>
+          <t>174544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -10198,32 +10198,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10233,32 +10233,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>76916</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>62787</t>
+          <t>74029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>108256</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10268,32 +10268,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82065</t>
+          <t>92223</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129773</t>
+          <t>139045</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -10315,32 +10315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2005606</t>
+          <t>2193318</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1560358</t>
+          <t>2126123</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2185806</t>
+          <t>2248415</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10350,32 +10350,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2374681</t>
+          <t>2362815</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2235527</t>
+          <t>2307917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2568334</t>
+          <t>2411357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10385,32 +10385,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4380288</t>
+          <t>4556133</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3878975</t>
+          <t>4477450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4614320</t>
+          <t>4635134</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -10428,17 +10428,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>197679</t>
+          <t>201393</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>150620</t>
+          <t>174058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>231520</t>
+          <t>230072</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10463,32 +10463,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>219192</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>170554</t>
+          <t>194271</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>236938</t>
+          <t>245707</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10498,32 +10498,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>404819</t>
+          <t>420585</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>345031</t>
+          <t>383861</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>452661</t>
+          <t>462134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -10541,69 +10541,69 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>818434</t>
+          <t>616802</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599932</t>
+          <t>566352</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1397069</t>
+          <t>676982</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>601631</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>566020</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>645421</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>17,8%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>552599</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>445836</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>611692</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1405</t>
@@ -10611,32 +10611,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1371033</t>
+          <t>1218433</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1137263</t>
+          <t>1152162</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2124200</t>
+          <t>1286289</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -10654,32 +10654,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>421360</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>266319</t>
+          <t>380745</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>399716</t>
+          <t>470540</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>435431</t>
+          <t>442443</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>351857</t>
+          <t>409602</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>679644</t>
+          <t>483304</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10724,32 +10724,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>783760</t>
+          <t>863804</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>667398</t>
+          <t>813983</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>978106</t>
+          <t>929725</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
